--- a/docs/collections/tashiro/metadata/data.xlsx
+++ b/docs/collections/tashiro/metadata/data.xlsx
@@ -347,7 +347,7 @@
     <t>沖縄島諸祭神祝女類別表 ; 沖縄島祝女佩用勾玉實檢圖解</t>
   </si>
   <si>
-    <t>オキナワジマ ショサイシン シュクジョ ルイベツヒョウ ; オキナワジマ シュクジョ ハイヨウ マガタマ ジッケン ズカイ</t>
+    <t>オキナワジマ ショサイシン ノロ ルイベツヒョウ ; オキナワジマ ノロ ハイヨウ マガタマ ジッケン ズカイ</t>
   </si>
   <si>
     <t>952:516</t>
